--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95989105</v>
+        <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78942</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6426</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408705.8307514756</v>
+        <v>408510</v>
       </c>
       <c r="R2" t="n">
-        <v>6704766.999019728</v>
+        <v>6704622</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +760,60 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95989099</v>
+        <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408573.3624558236</v>
+        <v>408505</v>
       </c>
       <c r="R3" t="n">
-        <v>6704628.746969437</v>
+        <v>6704606</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,44 +857,39 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95989100</v>
+        <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,17 +900,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408573.3624558236</v>
+        <v>408490</v>
       </c>
       <c r="R4" t="n">
-        <v>6704628.746969437</v>
+        <v>6704576</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95989102</v>
+        <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408671.8137017373</v>
+        <v>408529</v>
       </c>
       <c r="R5" t="n">
-        <v>6704750.589711819</v>
+        <v>6704622</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95989101</v>
+        <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408573.3624558236</v>
+        <v>408490</v>
       </c>
       <c r="R6" t="n">
-        <v>6704628.746969437</v>
+        <v>6704557</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,15 +1148,2512 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132139039</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79276</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>408501</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6704600</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132139004</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79895</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>408498</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6704606</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132139041</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79276</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>408476</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6704555</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95989105</v>
+      </c>
+      <c r="B10" t="n">
+        <v>73631</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>408705.8307514756</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6704766.999019728</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>anders tedeholm</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95989099</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78596</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>408573.3624558236</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6704628.746969437</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95989100</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78602</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>408573.3624558236</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6704628.746969437</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95989102</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>408671.8137017373</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6704750.589711819</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95989101</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78569</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>408573.3624558236</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6704628.746969437</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132139047</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80416</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>408580</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6704639</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132139048</v>
+      </c>
+      <c r="B16" t="n">
+        <v>83248</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>308</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>408665</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6704731</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132139000</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>408698</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6704778</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132139049</v>
+      </c>
+      <c r="B18" t="n">
+        <v>83248</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>308</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Brunpudrad nållav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracillima</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>408548</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6704620</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132139002</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91811</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>408661</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6704720</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132139035</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79276</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>408560</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6704640</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132139011</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>408658</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6704718</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132139017</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96286</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>408671</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6704743</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132139029</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80341</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>408613</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6704660</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132139027</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80381</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>408578</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6704638</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132139008</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>408709</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6704790</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132139020</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79034</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>408630</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6704686</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132138998</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97294</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>53</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>408698</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6704778</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132139030</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79033</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>408590</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6704639</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132139024</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80381</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>408613</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6704660</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132138999</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97294</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>53</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>408659</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6704715</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132139028</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97921</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>408660</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6704737</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139004</v>
+        <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79895</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408498</v>
+        <v>408476</v>
       </c>
       <c r="R8" t="n">
-        <v>6704606</v>
+        <v>6704555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139041</v>
+        <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79276</v>
+        <v>79895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408476</v>
+        <v>408498</v>
       </c>
       <c r="R9" t="n">
-        <v>6704555</v>
+        <v>6704606</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>80381</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R24" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139008</v>
+        <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>80381</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408709</v>
+        <v>408578</v>
       </c>
       <c r="R25" t="n">
-        <v>6704790</v>
+        <v>6704638</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>80381</v>
+        <v>97294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R29" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>97294</v>
+        <v>80381</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R30" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139041</v>
+        <v>132139004</v>
       </c>
       <c r="B8" t="n">
-        <v>79276</v>
+        <v>79895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408476</v>
+        <v>408498</v>
       </c>
       <c r="R8" t="n">
-        <v>6704555</v>
+        <v>6704606</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139004</v>
+        <v>132139041</v>
       </c>
       <c r="B9" t="n">
-        <v>79895</v>
+        <v>79276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408498</v>
+        <v>408476</v>
       </c>
       <c r="R9" t="n">
-        <v>6704606</v>
+        <v>6704555</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139049</v>
+        <v>132139002</v>
       </c>
       <c r="B18" t="n">
-        <v>83248</v>
+        <v>91811</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408548</v>
+        <v>408661</v>
       </c>
       <c r="R18" t="n">
-        <v>6704620</v>
+        <v>6704720</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139002</v>
+        <v>132139049</v>
       </c>
       <c r="B19" t="n">
-        <v>91811</v>
+        <v>83248</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408661</v>
+        <v>408548</v>
       </c>
       <c r="R19" t="n">
-        <v>6704720</v>
+        <v>6704620</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B22" t="n">
-        <v>96286</v>
+        <v>80341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R22" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B23" t="n">
-        <v>80341</v>
+        <v>96286</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R23" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139004</v>
+        <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79895</v>
+        <v>79276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408498</v>
+        <v>408476</v>
       </c>
       <c r="R8" t="n">
-        <v>6704606</v>
+        <v>6704555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139041</v>
+        <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79276</v>
+        <v>79895</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408476</v>
+        <v>408498</v>
       </c>
       <c r="R9" t="n">
-        <v>6704555</v>
+        <v>6704606</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139008</v>
+        <v>132139027</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>80381</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408709</v>
+        <v>408578</v>
       </c>
       <c r="R24" t="n">
-        <v>6704790</v>
+        <v>6704638</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B25" t="n">
-        <v>80381</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R25" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B29" t="n">
-        <v>97294</v>
+        <v>80381</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R29" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B30" t="n">
-        <v>80381</v>
+        <v>97294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R30" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>78981</v>
+        <v>78983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132139039</v>
       </c>
       <c r="B7" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>132139047</v>
       </c>
       <c r="B15" t="n">
-        <v>80455</v>
+        <v>80457</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>132139049</v>
       </c>
       <c r="B18" t="n">
-        <v>83287</v>
+        <v>83289</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>132139002</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>132139035</v>
       </c>
       <c r="B20" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>132139017</v>
       </c>
       <c r="B22" t="n">
-        <v>96327</v>
+        <v>96330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>132139029</v>
       </c>
       <c r="B23" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>132139020</v>
       </c>
       <c r="B26" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>132139030</v>
       </c>
       <c r="B28" t="n">
-        <v>79072</v>
+        <v>79074</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>97335</v>
+        <v>97338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97962</v>
+        <v>97965</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B29" t="n">
-        <v>97338</v>
+        <v>80422</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R29" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B30" t="n">
-        <v>80422</v>
+        <v>97338</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R30" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B22" t="n">
-        <v>96330</v>
+        <v>80382</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R22" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B23" t="n">
-        <v>80382</v>
+        <v>96330</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R23" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>80422</v>
+        <v>97338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R29" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>97338</v>
+        <v>80422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R30" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>80422</v>
+        <v>97338</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R29" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>97338</v>
+        <v>80422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R30" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>78983</v>
+        <v>78985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132139039</v>
       </c>
       <c r="B7" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79936</v>
+        <v>79938</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>132139047</v>
       </c>
       <c r="B15" t="n">
-        <v>80457</v>
+        <v>80459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83289</v>
+        <v>83291</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139049</v>
+        <v>132139002</v>
       </c>
       <c r="B18" t="n">
-        <v>83289</v>
+        <v>91861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408548</v>
+        <v>408661</v>
       </c>
       <c r="R18" t="n">
-        <v>6704620</v>
+        <v>6704720</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139002</v>
+        <v>132139049</v>
       </c>
       <c r="B19" t="n">
-        <v>91855</v>
+        <v>83291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408661</v>
+        <v>408548</v>
       </c>
       <c r="R19" t="n">
-        <v>6704720</v>
+        <v>6704620</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2499,7 +2499,7 @@
         <v>132139035</v>
       </c>
       <c r="B20" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B22" t="n">
-        <v>80382</v>
+        <v>96338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R22" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B23" t="n">
-        <v>96330</v>
+        <v>80384</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R23" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
         <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>132139020</v>
       </c>
       <c r="B26" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97338</v>
+        <v>97346</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>132139030</v>
       </c>
       <c r="B28" t="n">
-        <v>79074</v>
+        <v>79076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B29" t="n">
-        <v>97338</v>
+        <v>80424</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R29" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B30" t="n">
-        <v>80422</v>
+        <v>97346</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R30" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97965</v>
+        <v>97973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139008</v>
+        <v>132139020</v>
       </c>
       <c r="B24" t="n">
-        <v>91898</v>
+        <v>79077</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408709</v>
+        <v>408630</v>
       </c>
       <c r="R24" t="n">
-        <v>6704790</v>
+        <v>6704686</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B25" t="n">
-        <v>80424</v>
+        <v>91898</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R25" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139020</v>
+        <v>132139027</v>
       </c>
       <c r="B26" t="n">
-        <v>79077</v>
+        <v>80424</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408630</v>
+        <v>408578</v>
       </c>
       <c r="R26" t="n">
-        <v>6704686</v>
+        <v>6704638</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>80424</v>
+        <v>97346</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R29" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>97346</v>
+        <v>80424</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R30" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>78985</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132139039</v>
       </c>
       <c r="B7" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79938</v>
+        <v>79946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>132139047</v>
       </c>
       <c r="B15" t="n">
-        <v>80459</v>
+        <v>80467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>132139002</v>
       </c>
       <c r="B18" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,7 +2402,7 @@
         <v>132139049</v>
       </c>
       <c r="B19" t="n">
-        <v>83291</v>
+        <v>83299</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>132139035</v>
       </c>
       <c r="B20" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B22" t="n">
-        <v>96338</v>
+        <v>80392</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R22" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B23" t="n">
-        <v>80384</v>
+        <v>96348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R23" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
         <v>132139020</v>
       </c>
       <c r="B24" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139008</v>
+        <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>91898</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408709</v>
+        <v>408578</v>
       </c>
       <c r="R25" t="n">
-        <v>6704790</v>
+        <v>6704638</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B26" t="n">
-        <v>80424</v>
+        <v>91908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R26" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>132139030</v>
       </c>
       <c r="B28" t="n">
-        <v>79076</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>97346</v>
+        <v>97356</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97973</v>
+        <v>97983</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139020</v>
+        <v>132139027</v>
       </c>
       <c r="B24" t="n">
-        <v>79085</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408630</v>
+        <v>408578</v>
       </c>
       <c r="R24" t="n">
-        <v>6704686</v>
+        <v>6704638</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B25" t="n">
-        <v>80432</v>
+        <v>91908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R25" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139008</v>
+        <v>132139020</v>
       </c>
       <c r="B26" t="n">
-        <v>91908</v>
+        <v>79085</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408709</v>
+        <v>408630</v>
       </c>
       <c r="R26" t="n">
-        <v>6704790</v>
+        <v>6704686</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>132139002</v>
       </c>
       <c r="B18" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         <v>132139017</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
+        <v>96350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>132139008</v>
       </c>
       <c r="B25" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>97356</v>
+        <v>97358</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97983</v>
+        <v>97985</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>80432</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R24" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139008</v>
+        <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>91909</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408709</v>
+        <v>408578</v>
       </c>
       <c r="R25" t="n">
-        <v>6704790</v>
+        <v>6704638</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>78993</v>
+        <v>78994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132139039</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139041</v>
+        <v>132139004</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>79947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408476</v>
+        <v>408498</v>
       </c>
       <c r="R8" t="n">
-        <v>6704555</v>
+        <v>6704606</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139004</v>
+        <v>132139041</v>
       </c>
       <c r="B9" t="n">
-        <v>79946</v>
+        <v>79328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408498</v>
+        <v>408476</v>
       </c>
       <c r="R9" t="n">
-        <v>6704606</v>
+        <v>6704555</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2014,7 +2014,7 @@
         <v>132139047</v>
       </c>
       <c r="B15" t="n">
-        <v>80467</v>
+        <v>80468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83299</v>
+        <v>83300</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139002</v>
+        <v>132139049</v>
       </c>
       <c r="B18" t="n">
-        <v>91872</v>
+        <v>83300</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408661</v>
+        <v>408548</v>
       </c>
       <c r="R18" t="n">
-        <v>6704720</v>
+        <v>6704620</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139049</v>
+        <v>132139002</v>
       </c>
       <c r="B19" t="n">
-        <v>83299</v>
+        <v>91873</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408548</v>
+        <v>408661</v>
       </c>
       <c r="R19" t="n">
-        <v>6704620</v>
+        <v>6704720</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2499,7 +2499,7 @@
         <v>132139035</v>
       </c>
       <c r="B20" t="n">
-        <v>79327</v>
+        <v>79328</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91909</v>
+        <v>91910</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B22" t="n">
-        <v>80392</v>
+        <v>96351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R22" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B23" t="n">
-        <v>96350</v>
+        <v>80393</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R23" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139008</v>
+        <v>132139027</v>
       </c>
       <c r="B24" t="n">
-        <v>91909</v>
+        <v>80433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408709</v>
+        <v>408578</v>
       </c>
       <c r="R24" t="n">
-        <v>6704790</v>
+        <v>6704638</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B25" t="n">
-        <v>80432</v>
+        <v>91910</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R25" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3081,7 +3081,7 @@
         <v>132139020</v>
       </c>
       <c r="B26" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>132139030</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79085</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>97358</v>
+        <v>97359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>80432</v>
+        <v>80433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139004</v>
+        <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79947</v>
+        <v>79328</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408498</v>
+        <v>408476</v>
       </c>
       <c r="R8" t="n">
-        <v>6704606</v>
+        <v>6704555</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139041</v>
+        <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79328</v>
+        <v>79947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408476</v>
+        <v>408498</v>
       </c>
       <c r="R9" t="n">
-        <v>6704555</v>
+        <v>6704606</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83300</v>
+        <v>83302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139049</v>
+        <v>132139002</v>
       </c>
       <c r="B18" t="n">
-        <v>83300</v>
+        <v>91875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408548</v>
+        <v>408661</v>
       </c>
       <c r="R18" t="n">
-        <v>6704620</v>
+        <v>6704720</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139002</v>
+        <v>132139049</v>
       </c>
       <c r="B19" t="n">
-        <v>91873</v>
+        <v>83302</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408661</v>
+        <v>408548</v>
       </c>
       <c r="R19" t="n">
-        <v>6704720</v>
+        <v>6704620</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91910</v>
+        <v>91912</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>132139017</v>
       </c>
       <c r="B22" t="n">
-        <v>96351</v>
+        <v>96353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2884,10 +2884,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139027</v>
+        <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>80433</v>
+        <v>91912</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,21 +2895,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2919,10 +2919,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408578</v>
+        <v>408709</v>
       </c>
       <c r="R24" t="n">
-        <v>6704638</v>
+        <v>6704790</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139008</v>
+        <v>132139020</v>
       </c>
       <c r="B25" t="n">
-        <v>91910</v>
+        <v>79086</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408709</v>
+        <v>408630</v>
       </c>
       <c r="R25" t="n">
-        <v>6704790</v>
+        <v>6704686</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139020</v>
+        <v>132139027</v>
       </c>
       <c r="B26" t="n">
-        <v>79086</v>
+        <v>80433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408630</v>
+        <v>408578</v>
       </c>
       <c r="R26" t="n">
-        <v>6704686</v>
+        <v>6704638</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B29" t="n">
-        <v>97359</v>
+        <v>80433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R29" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B30" t="n">
-        <v>80433</v>
+        <v>97361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R30" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97986</v>
+        <v>97988</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132139044</v>
       </c>
       <c r="B2" t="n">
-        <v>78994</v>
+        <v>78995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132139038</v>
       </c>
       <c r="B3" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132139040</v>
       </c>
       <c r="B4" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>132139036</v>
       </c>
       <c r="B5" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>132139037</v>
       </c>
       <c r="B6" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>132139039</v>
       </c>
       <c r="B7" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>132139041</v>
       </c>
       <c r="B8" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>132139004</v>
       </c>
       <c r="B9" t="n">
-        <v>79947</v>
+        <v>79948</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
         <v>132139047</v>
       </c>
       <c r="B15" t="n">
-        <v>80468</v>
+        <v>80469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>132139048</v>
       </c>
       <c r="B16" t="n">
-        <v>83302</v>
+        <v>83303</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>132139000</v>
       </c>
       <c r="B17" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2302,32 +2302,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139002</v>
+        <v>132139049</v>
       </c>
       <c r="B18" t="n">
-        <v>91875</v>
+        <v>83303</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2337,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408661</v>
+        <v>408548</v>
       </c>
       <c r="R18" t="n">
-        <v>6704720</v>
+        <v>6704620</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2399,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139049</v>
+        <v>132139002</v>
       </c>
       <c r="B19" t="n">
-        <v>83302</v>
+        <v>91876</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408548</v>
+        <v>408661</v>
       </c>
       <c r="R19" t="n">
-        <v>6704620</v>
+        <v>6704720</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2499,7 +2499,7 @@
         <v>132139035</v>
       </c>
       <c r="B20" t="n">
-        <v>79328</v>
+        <v>79329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
         <v>132139011</v>
       </c>
       <c r="B21" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2690,10 +2690,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139017</v>
+        <v>132139029</v>
       </c>
       <c r="B22" t="n">
-        <v>96353</v>
+        <v>80394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2701,21 +2701,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>229497</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2725,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408671</v>
+        <v>408613</v>
       </c>
       <c r="R22" t="n">
-        <v>6704743</v>
+        <v>6704660</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,10 +2787,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139029</v>
+        <v>132139017</v>
       </c>
       <c r="B23" t="n">
-        <v>80393</v>
+        <v>96354</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2798,21 +2798,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>2813</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2822,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408613</v>
+        <v>408671</v>
       </c>
       <c r="R23" t="n">
-        <v>6704660</v>
+        <v>6704743</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2887,7 +2887,7 @@
         <v>132139008</v>
       </c>
       <c r="B24" t="n">
-        <v>91912</v>
+        <v>91913</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139020</v>
+        <v>132139027</v>
       </c>
       <c r="B25" t="n">
-        <v>79086</v>
+        <v>80434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2992,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +3016,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408630</v>
+        <v>408578</v>
       </c>
       <c r="R25" t="n">
-        <v>6704686</v>
+        <v>6704638</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3078,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139027</v>
+        <v>132139020</v>
       </c>
       <c r="B26" t="n">
-        <v>80433</v>
+        <v>79087</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3089,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408578</v>
+        <v>408630</v>
       </c>
       <c r="R26" t="n">
-        <v>6704638</v>
+        <v>6704686</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3178,7 +3178,7 @@
         <v>132138998</v>
       </c>
       <c r="B27" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>132139030</v>
       </c>
       <c r="B28" t="n">
-        <v>79085</v>
+        <v>79086</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3369,10 +3369,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139024</v>
+        <v>132138999</v>
       </c>
       <c r="B29" t="n">
-        <v>80433</v>
+        <v>97362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3380,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3404,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408613</v>
+        <v>408659</v>
       </c>
       <c r="R29" t="n">
-        <v>6704660</v>
+        <v>6704715</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132138999</v>
+        <v>132139024</v>
       </c>
       <c r="B30" t="n">
-        <v>97361</v>
+        <v>80434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3477,21 +3477,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3501,10 +3501,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408659</v>
+        <v>408613</v>
       </c>
       <c r="R30" t="n">
-        <v>6704715</v>
+        <v>6704660</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3566,7 +3566,7 @@
         <v>132139028</v>
       </c>
       <c r="B31" t="n">
-        <v>97988</v>
+        <v>97989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132139044</v>
+        <v>132138997</v>
       </c>
       <c r="B2" t="n">
-        <v>78995</v>
+        <v>97435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>408510</v>
+        <v>408732</v>
       </c>
       <c r="R2" t="n">
-        <v>6704622</v>
+        <v>6704747</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132139038</v>
+        <v>132138998</v>
       </c>
       <c r="B3" t="n">
-        <v>79329</v>
+        <v>97435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>408505</v>
+        <v>408698</v>
       </c>
       <c r="R3" t="n">
-        <v>6704606</v>
+        <v>6704778</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132139040</v>
+        <v>132138999</v>
       </c>
       <c r="B4" t="n">
-        <v>79329</v>
+        <v>97435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>408490</v>
+        <v>408659</v>
       </c>
       <c r="R4" t="n">
-        <v>6704576</v>
+        <v>6704715</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132139036</v>
+        <v>132139048</v>
       </c>
       <c r="B5" t="n">
-        <v>79329</v>
+        <v>83350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>408529</v>
+        <v>408665</v>
       </c>
       <c r="R5" t="n">
-        <v>6704622</v>
+        <v>6704731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132139037</v>
+        <v>132139049</v>
       </c>
       <c r="B6" t="n">
-        <v>79329</v>
+        <v>83350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>408490</v>
+        <v>408548</v>
       </c>
       <c r="R6" t="n">
-        <v>6704557</v>
+        <v>6704620</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132139039</v>
+        <v>132139044</v>
       </c>
       <c r="B7" t="n">
-        <v>79329</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>408501</v>
+        <v>408510</v>
       </c>
       <c r="R7" t="n">
-        <v>6704600</v>
+        <v>6704622</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132139041</v>
+        <v>132139045</v>
       </c>
       <c r="B8" t="n">
-        <v>79329</v>
+        <v>89354</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>408476</v>
+        <v>408732</v>
       </c>
       <c r="R8" t="n">
-        <v>6704555</v>
+        <v>6704746</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132139004</v>
+        <v>132139007</v>
       </c>
       <c r="B9" t="n">
-        <v>79948</v>
+        <v>91974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>408498</v>
+        <v>408740</v>
       </c>
       <c r="R9" t="n">
-        <v>6704606</v>
+        <v>6704752</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1451,53 +1451,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95989105</v>
+        <v>132139008</v>
       </c>
       <c r="B10" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>408705.8307514756</v>
+        <v>408709</v>
       </c>
       <c r="R10" t="n">
-        <v>6704766.999019728</v>
+        <v>6704790</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1521,22 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1551,65 +1536,60 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95989099</v>
+        <v>132139011</v>
       </c>
       <c r="B11" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>408573.3624558236</v>
+        <v>408658</v>
       </c>
       <c r="R11" t="n">
-        <v>6704628.746969437</v>
+        <v>6704718</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,65 +1633,60 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>95989100</v>
+        <v>132139018</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>408573.3624558236</v>
+        <v>408730</v>
       </c>
       <c r="R12" t="n">
-        <v>6704628.746969437</v>
+        <v>6704746</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1745,22 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,71 +1724,67 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95989102</v>
+        <v>132139017</v>
       </c>
       <c r="B13" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96425</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2813</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>408671.8137017373</v>
+        <v>408671</v>
       </c>
       <c r="R13" t="n">
-        <v>6704750.589711819</v>
+        <v>6704743</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1857,22 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,65 +1828,60 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95989101</v>
+        <v>132139000</v>
       </c>
       <c r="B14" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>408573.3624558236</v>
+        <v>408698</v>
       </c>
       <c r="R14" t="n">
-        <v>6704628.746969437</v>
+        <v>6704778</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1969,22 +1905,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1999,22 +1925,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132139047</v>
+        <v>132139002</v>
       </c>
       <c r="B15" t="n">
-        <v>80469</v>
+        <v>91937</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2022,21 +1948,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2046,10 +1972,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>408580</v>
+        <v>408661</v>
       </c>
       <c r="R15" t="n">
-        <v>6704639</v>
+        <v>6704720</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2108,32 +2034,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132139048</v>
+        <v>132139034</v>
       </c>
       <c r="B16" t="n">
-        <v>83303</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408665</v>
+        <v>408719</v>
       </c>
       <c r="R16" t="n">
-        <v>6704731</v>
+        <v>6704792</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2205,32 +2131,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132139000</v>
+        <v>132139035</v>
       </c>
       <c r="B17" t="n">
-        <v>91876</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2240,10 +2166,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408698</v>
+        <v>408560</v>
       </c>
       <c r="R17" t="n">
-        <v>6704778</v>
+        <v>6704640</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2302,32 +2228,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139049</v>
+        <v>132139036</v>
       </c>
       <c r="B18" t="n">
-        <v>83303</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2337,10 +2263,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408548</v>
+        <v>408529</v>
       </c>
       <c r="R18" t="n">
-        <v>6704620</v>
+        <v>6704622</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2399,32 +2325,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139002</v>
+        <v>132139037</v>
       </c>
       <c r="B19" t="n">
-        <v>91876</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2434,10 +2360,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408661</v>
+        <v>408490</v>
       </c>
       <c r="R19" t="n">
-        <v>6704720</v>
+        <v>6704557</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2496,14 +2422,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132139035</v>
+        <v>132139038</v>
       </c>
       <c r="B20" t="n">
-        <v>79329</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2531,10 +2457,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408560</v>
+        <v>408505</v>
       </c>
       <c r="R20" t="n">
-        <v>6704640</v>
+        <v>6704606</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2593,32 +2519,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132139011</v>
+        <v>132139039</v>
       </c>
       <c r="B21" t="n">
-        <v>91913</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2628,10 +2554,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408658</v>
+        <v>408501</v>
       </c>
       <c r="R21" t="n">
-        <v>6704718</v>
+        <v>6704600</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2690,32 +2616,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139017</v>
+        <v>132139040</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2813</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2725,10 +2651,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408671</v>
+        <v>408490</v>
       </c>
       <c r="R22" t="n">
-        <v>6704743</v>
+        <v>6704576</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2787,32 +2713,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139029</v>
+        <v>132139041</v>
       </c>
       <c r="B23" t="n">
-        <v>80394</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2822,10 +2748,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408613</v>
+        <v>408476</v>
       </c>
       <c r="R23" t="n">
-        <v>6704660</v>
+        <v>6704555</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2884,10 +2810,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132139020</v>
+        <v>95989105</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>75428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2895,37 +2821,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408630</v>
+        <v>408706</v>
       </c>
       <c r="R24" t="n">
-        <v>6704686</v>
+        <v>6704767</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2949,12 +2875,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2969,22 +2895,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139008</v>
+        <v>132139030</v>
       </c>
       <c r="B25" t="n">
-        <v>91913</v>
+        <v>79130</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2992,21 +2918,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3016,10 +2942,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408709</v>
+        <v>408590</v>
       </c>
       <c r="R25" t="n">
-        <v>6704790</v>
+        <v>6704639</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3078,10 +3004,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139027</v>
+        <v>132139004</v>
       </c>
       <c r="B26" t="n">
-        <v>80434</v>
+        <v>79992</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3089,21 +3015,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3039,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408578</v>
+        <v>408498</v>
       </c>
       <c r="R26" t="n">
-        <v>6704638</v>
+        <v>6704606</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3175,10 +3101,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132138998</v>
+        <v>95989101</v>
       </c>
       <c r="B27" t="n">
-        <v>97362</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3186,37 +3112,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408698</v>
+        <v>408574</v>
       </c>
       <c r="R27" t="n">
-        <v>6704778</v>
+        <v>6704628</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3240,12 +3166,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3260,22 +3186,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132139030</v>
+        <v>95989102</v>
       </c>
       <c r="B28" t="n">
-        <v>79086</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,37 +3209,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408590</v>
+        <v>408672</v>
       </c>
       <c r="R28" t="n">
-        <v>6704639</v>
+        <v>6704751</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3337,12 +3263,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3357,22 +3283,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132138999</v>
+        <v>132139021</v>
       </c>
       <c r="B29" t="n">
-        <v>97362</v>
+        <v>80488</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,21 +3306,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3404,10 +3330,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408659</v>
+        <v>408633</v>
       </c>
       <c r="R29" t="n">
-        <v>6704715</v>
+        <v>6704676</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3466,10 +3392,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139024</v>
+        <v>132139023</v>
       </c>
       <c r="B30" t="n">
-        <v>80434</v>
+        <v>80488</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3501,10 +3427,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>408613</v>
+        <v>408633</v>
       </c>
       <c r="R30" t="n">
-        <v>6704660</v>
+        <v>6704658</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3563,30 +3489,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132139028</v>
+        <v>132139024</v>
       </c>
       <c r="B31" t="n">
-        <v>97989</v>
+        <v>80488</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>224363</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3594,10 +3524,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408660</v>
+        <v>408613</v>
       </c>
       <c r="R31" t="n">
-        <v>6704737</v>
+        <v>6704660</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3638,7 +3568,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3654,6 +3583,880 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132139027</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>408578</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6704638</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>95989099</v>
+      </c>
+      <c r="B33" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>408574</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6704628</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132139014</v>
+      </c>
+      <c r="B34" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>408612</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6704652</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>95989100</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ö om Väberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>408574</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6704628</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2021-09-08</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>anders tedeholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132139047</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80499</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>408580</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6704639</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132139028</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98062</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>408660</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6704737</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132139020</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>408630</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6704686</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132139029</v>
+      </c>
+      <c r="B39" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>408613</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6704660</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>100238507</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>408680</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6704710</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Nina Marliden</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Nina Marliden, Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16074-2026 artfynd.xlsx
+++ b/artfynd/A 16074-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2034,7 +2034,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132139034</v>
+        <v>132139033</v>
       </c>
       <c r="B16" t="n">
         <v>79373</v>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>408719</v>
+        <v>408746</v>
       </c>
       <c r="R16" t="n">
-        <v>6704792</v>
+        <v>6704780</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2113,6 +2113,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2131,7 +2132,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132139035</v>
+        <v>132139034</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2166,10 +2167,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>408560</v>
+        <v>408719</v>
       </c>
       <c r="R17" t="n">
-        <v>6704640</v>
+        <v>6704792</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2228,7 +2229,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132139036</v>
+        <v>132139035</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2263,10 +2264,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>408529</v>
+        <v>408560</v>
       </c>
       <c r="R18" t="n">
-        <v>6704622</v>
+        <v>6704640</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2325,7 +2326,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132139037</v>
+        <v>132139036</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2360,10 +2361,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>408490</v>
+        <v>408529</v>
       </c>
       <c r="R19" t="n">
-        <v>6704557</v>
+        <v>6704622</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2422,7 +2423,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132139038</v>
+        <v>132139037</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2457,10 +2458,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>408505</v>
+        <v>408490</v>
       </c>
       <c r="R20" t="n">
-        <v>6704606</v>
+        <v>6704557</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2519,7 +2520,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132139039</v>
+        <v>132139038</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2554,10 +2555,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>408501</v>
+        <v>408505</v>
       </c>
       <c r="R21" t="n">
-        <v>6704600</v>
+        <v>6704606</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2616,7 +2617,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132139040</v>
+        <v>132139039</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2651,10 +2652,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>408490</v>
+        <v>408501</v>
       </c>
       <c r="R22" t="n">
-        <v>6704576</v>
+        <v>6704600</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2713,7 +2714,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132139041</v>
+        <v>132139040</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2748,10 +2749,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>408476</v>
+        <v>408490</v>
       </c>
       <c r="R23" t="n">
-        <v>6704555</v>
+        <v>6704576</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -2810,48 +2811,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>95989105</v>
+        <v>132139041</v>
       </c>
       <c r="B24" t="n">
-        <v>75428</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6426</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>408706</v>
+        <v>408476</v>
       </c>
       <c r="R24" t="n">
-        <v>6704767</v>
+        <v>6704555</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2875,12 +2876,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2895,22 +2896,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132139030</v>
+        <v>95989105</v>
       </c>
       <c r="B25" t="n">
-        <v>79130</v>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2918,37 +2919,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>408590</v>
+        <v>408706</v>
       </c>
       <c r="R25" t="n">
-        <v>6704639</v>
+        <v>6704767</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2972,12 +2973,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -2992,22 +2993,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132139004</v>
+        <v>132139030</v>
       </c>
       <c r="B26" t="n">
-        <v>79992</v>
+        <v>79130</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3015,21 +3016,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3039,10 +3040,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>408498</v>
+        <v>408590</v>
       </c>
       <c r="R26" t="n">
-        <v>6704606</v>
+        <v>6704639</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3101,10 +3102,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>95989101</v>
+        <v>132139004</v>
       </c>
       <c r="B27" t="n">
-        <v>80432</v>
+        <v>79992</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3112,37 +3113,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>408574</v>
+        <v>408498</v>
       </c>
       <c r="R27" t="n">
-        <v>6704628</v>
+        <v>6704606</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3166,12 +3167,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3186,19 +3187,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>95989102</v>
+        <v>95989101</v>
       </c>
       <c r="B28" t="n">
         <v>80432</v>
@@ -3233,10 +3234,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>408672</v>
+        <v>408574</v>
       </c>
       <c r="R28" t="n">
-        <v>6704751</v>
+        <v>6704628</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3295,10 +3296,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132139021</v>
+        <v>95989102</v>
       </c>
       <c r="B29" t="n">
-        <v>80488</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3326,17 +3327,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>408633</v>
+        <v>408672</v>
       </c>
       <c r="R29" t="n">
-        <v>6704676</v>
+        <v>6704751</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3360,12 +3361,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3380,19 +3381,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132139023</v>
+        <v>132139021</v>
       </c>
       <c r="B30" t="n">
         <v>80488</v>
@@ -3430,7 +3431,7 @@
         <v>408633</v>
       </c>
       <c r="R30" t="n">
-        <v>6704658</v>
+        <v>6704676</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3489,7 +3490,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132139024</v>
+        <v>132139023</v>
       </c>
       <c r="B31" t="n">
         <v>80488</v>
@@ -3524,10 +3525,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>408613</v>
+        <v>408633</v>
       </c>
       <c r="R31" t="n">
-        <v>6704660</v>
+        <v>6704658</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3586,7 +3587,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132139027</v>
+        <v>132139024</v>
       </c>
       <c r="B32" t="n">
         <v>80488</v>
@@ -3621,10 +3622,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>408578</v>
+        <v>408613</v>
       </c>
       <c r="R32" t="n">
-        <v>6704638</v>
+        <v>6704660</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3683,48 +3684,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>95989099</v>
+        <v>132139027</v>
       </c>
       <c r="B33" t="n">
-        <v>80461</v>
+        <v>80488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>408574</v>
+        <v>408578</v>
       </c>
       <c r="R33" t="n">
-        <v>6704628</v>
+        <v>6704638</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3748,12 +3749,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3768,22 +3769,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132139014</v>
+        <v>95989099</v>
       </c>
       <c r="B34" t="n">
-        <v>80493</v>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,17 +3812,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>408612</v>
+        <v>408574</v>
       </c>
       <c r="R34" t="n">
-        <v>6704652</v>
+        <v>6704628</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3845,12 +3846,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3865,22 +3866,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>95989100</v>
+        <v>132139014</v>
       </c>
       <c r="B35" t="n">
-        <v>80467</v>
+        <v>80493</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3888,37 +3889,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ö om Väberget, Vrm</t>
+          <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>408574</v>
+        <v>408612</v>
       </c>
       <c r="R35" t="n">
-        <v>6704628</v>
+        <v>6704652</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3942,12 +3943,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3962,22 +3963,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132139047</v>
+        <v>95989100</v>
       </c>
       <c r="B36" t="n">
-        <v>80499</v>
+        <v>80467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4005,17 +4006,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kampåsen, Vrm</t>
+          <t>Ö om Väberget, Vrm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>408580</v>
+        <v>408574</v>
       </c>
       <c r="R36" t="n">
-        <v>6704639</v>
+        <v>6704628</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4039,12 +4040,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4059,22 +4060,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Moa Björnberg Dillner</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132139028</v>
+        <v>132139047</v>
       </c>
       <c r="B37" t="n">
-        <v>98062</v>
+        <v>80499</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4082,19 +4083,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224363</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4102,10 +4107,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>408660</v>
+        <v>408580</v>
       </c>
       <c r="R37" t="n">
-        <v>6704737</v>
+        <v>6704639</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4146,7 +4151,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4165,34 +4169,30 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132139020</v>
+        <v>132139028</v>
       </c>
       <c r="B38" t="n">
-        <v>79131</v>
+        <v>98062</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>224363</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vanlig revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4200,10 +4200,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>408630</v>
+        <v>408660</v>
       </c>
       <c r="R38" t="n">
-        <v>6704686</v>
+        <v>6704737</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4244,6 +4244,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4262,32 +4263,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132139029</v>
+        <v>132139020</v>
       </c>
       <c r="B39" t="n">
-        <v>80438</v>
+        <v>79131</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229497</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4297,10 +4298,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>408613</v>
+        <v>408630</v>
       </c>
       <c r="R39" t="n">
-        <v>6704660</v>
+        <v>6704686</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4359,10 +4360,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>100238507</v>
+        <v>132139029</v>
       </c>
       <c r="B40" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4370,40 +4371,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>229748</v>
+        <v>229497</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kampåsen, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>408680</v>
+        <v>408613</v>
       </c>
       <c r="R40" t="n">
-        <v>6704710</v>
+        <v>6704660</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4427,12 +4425,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4441,22 +4439,122 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>100238507</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kampåsen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>408680</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6704710</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2022-04-16</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
           <t>Nina Marliden</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX41" t="inlineStr">
         <is>
           <t>Nina Marliden, Marika Sjödin</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
